--- a/plantillas/PLANES.xlsx
+++ b/plantillas/PLANES.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1648" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1648" uniqueCount="227">
   <si>
     <t>Semestre</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Núcleo</t>
   </si>
   <si>
-    <t>(MATE 1201 O MATE1  O MATS1 )</t>
+    <t>(MATE 1201 O MATE1  O MATS1 ) Y MATE 1203C*</t>
   </si>
   <si>
     <t>ISIS 1221</t>
@@ -114,7 +114,7 @@
     <t>CÁLCULO INTEGRAL CON EC. DIF.</t>
   </si>
   <si>
-    <t>(MATE 1203 O MATE 1204 O MATE 1212)</t>
+    <t>(MATE 1203 O MATE 1204 O MATE 1212) Y MATE 1214C*</t>
   </si>
   <si>
     <t>MATE 1105</t>
@@ -123,6 +123,9 @@
     <t>ALGEBRA LINEAL</t>
   </si>
   <si>
+    <t>(MATE 1203 O MATE 1204 O MATE 1212) Y MATE 1105C*</t>
+  </si>
+  <si>
     <t>FISI 1518</t>
   </si>
   <si>
@@ -171,7 +174,7 @@
     <t>CÁLCULO VECTORIAL</t>
   </si>
   <si>
-    <t>(   (   (MATE 1214 O MATE 1215) Y (MATE 1105 O MATE 1106)   ) O (MATE 1253 Y MATE 2711 Y MATE 1252)   )</t>
+    <t>(   (   (MATE 1214 O MATE 1215) Y (MATE 1105 O MATE 1106)   ) O (MATE 1253 Y MATE 2711 Y MATE 1252)   ) Y MATE 1207C*</t>
   </si>
   <si>
     <t>MATE 2210</t>
@@ -1556,7 +1559,7 @@
         <v>13</v>
       </c>
       <c r="F12" s="16" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G12" s="16" t="s">
         <v>10</v>
@@ -1567,10 +1570,10 @@
         <v>2</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D13" s="14">
         <v>3</v>
@@ -1579,7 +1582,7 @@
         <v>13</v>
       </c>
       <c r="F13" s="16" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G13" s="16" t="s">
         <v>10</v>
@@ -1590,10 +1593,10 @@
         <v>2</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D14" s="14">
         <v>2</v>
@@ -1616,7 +1619,7 @@
         <v>10</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D15" s="11">
         <f>SUM(D8:D14)</f>
@@ -1636,10 +1639,10 @@
         <v>3</v>
       </c>
       <c r="B16" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D16" s="1">
         <v>1</v>
@@ -1659,10 +1662,10 @@
         <v>3</v>
       </c>
       <c r="B17" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D17" s="1">
         <v>3</v>
@@ -1671,7 +1674,7 @@
         <v>13</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>10</v>
@@ -1682,10 +1685,10 @@
         <v>3</v>
       </c>
       <c r="B18" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D18" s="1">
         <v>3</v>
@@ -1694,7 +1697,7 @@
         <v>13</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>10</v>
@@ -1705,10 +1708,10 @@
         <v>3</v>
       </c>
       <c r="B19" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D19" s="1">
         <v>3</v>
@@ -1717,7 +1720,7 @@
         <v>13</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>10</v>
@@ -1728,10 +1731,10 @@
         <v>3</v>
       </c>
       <c r="B20" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D20" s="1">
         <v>2</v>
@@ -1740,7 +1743,7 @@
         <v>13</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>10</v>
@@ -1751,10 +1754,10 @@
         <v>3</v>
       </c>
       <c r="B21" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D21" s="1">
         <v>3</v>
@@ -1763,7 +1766,7 @@
         <v>13</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>10</v>
@@ -1800,7 +1803,7 @@
         <v>10</v>
       </c>
       <c r="C23" s="13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D23" s="11">
         <f>SUM(D16:D22)</f>
@@ -1820,10 +1823,10 @@
         <v>4</v>
       </c>
       <c r="B24" s="15" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D24" s="14">
         <v>2</v>
@@ -1832,7 +1835,7 @@
         <v>13</v>
       </c>
       <c r="F24" s="16" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G24" s="16" t="s">
         <v>10</v>
@@ -1843,10 +1846,10 @@
         <v>4</v>
       </c>
       <c r="B25" s="15" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C25" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D25" s="14">
         <v>3</v>
@@ -1855,7 +1858,7 @@
         <v>13</v>
       </c>
       <c r="F25" s="16" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G25" s="16" t="s">
         <v>10</v>
@@ -1866,10 +1869,10 @@
         <v>4</v>
       </c>
       <c r="B26" s="15" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C26" s="16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D26" s="14">
         <v>3</v>
@@ -1878,7 +1881,7 @@
         <v>13</v>
       </c>
       <c r="F26" s="16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G26" s="16" t="s">
         <v>10</v>
@@ -1889,10 +1892,10 @@
         <v>4</v>
       </c>
       <c r="B27" s="15" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C27" s="16" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D27" s="14">
         <v>3</v>
@@ -1901,7 +1904,7 @@
         <v>13</v>
       </c>
       <c r="F27" s="16" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G27" s="16" t="s">
         <v>10</v>
@@ -1912,10 +1915,10 @@
         <v>4</v>
       </c>
       <c r="B28" s="18" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C28" s="19" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D28" s="17">
         <v>3</v>
@@ -1961,7 +1964,7 @@
         <v>10</v>
       </c>
       <c r="C30" s="13" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D30" s="11">
         <f>SUM(D24:D29)</f>
@@ -1981,10 +1984,10 @@
         <v>5</v>
       </c>
       <c r="B31" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D31" s="1">
         <v>3</v>
@@ -1993,7 +1996,7 @@
         <v>13</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>10</v>
@@ -2004,10 +2007,10 @@
         <v>5</v>
       </c>
       <c r="B32" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D32" s="1">
         <v>3</v>
@@ -2016,7 +2019,7 @@
         <v>13</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>10</v>
@@ -2027,10 +2030,10 @@
         <v>5</v>
       </c>
       <c r="B33" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D33" s="1">
         <v>3</v>
@@ -2039,7 +2042,7 @@
         <v>13</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>10</v>
@@ -2050,10 +2053,10 @@
         <v>5</v>
       </c>
       <c r="B34" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D34" s="1">
         <v>3</v>
@@ -2062,7 +2065,7 @@
         <v>13</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>10</v>
@@ -2073,10 +2076,10 @@
         <v>5</v>
       </c>
       <c r="B35" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D35" s="1">
         <v>3</v>
@@ -2085,7 +2088,7 @@
         <v>13</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>10</v>
@@ -2096,10 +2099,10 @@
         <v>5</v>
       </c>
       <c r="B36" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D36" s="1">
         <v>3</v>
@@ -2122,7 +2125,7 @@
         <v>10</v>
       </c>
       <c r="C37" s="13" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D37" s="11">
         <f>SUM(D31:D36)</f>
@@ -2142,10 +2145,10 @@
         <v>6</v>
       </c>
       <c r="B38" s="18" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C38" s="19" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D38" s="17">
         <v>3</v>
@@ -2165,10 +2168,10 @@
         <v>6</v>
       </c>
       <c r="B39" s="15" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C39" s="16" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D39" s="14">
         <v>3</v>
@@ -2177,7 +2180,7 @@
         <v>13</v>
       </c>
       <c r="F39" s="16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G39" s="16" t="s">
         <v>10</v>
@@ -2188,10 +2191,10 @@
         <v>6</v>
       </c>
       <c r="B40" s="15" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C40" s="16" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D40" s="14">
         <v>3</v>
@@ -2200,7 +2203,7 @@
         <v>13</v>
       </c>
       <c r="F40" s="16" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G40" s="16" t="s">
         <v>10</v>
@@ -2211,10 +2214,10 @@
         <v>6</v>
       </c>
       <c r="B41" s="15" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C41" s="16" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D41" s="14">
         <v>2</v>
@@ -2223,7 +2226,7 @@
         <v>13</v>
       </c>
       <c r="F41" s="16" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G41" s="16" t="s">
         <v>10</v>
@@ -2234,10 +2237,10 @@
         <v>6</v>
       </c>
       <c r="B42" s="15" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C42" s="16" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D42" s="14">
         <v>3</v>
@@ -2257,16 +2260,16 @@
         <v>6</v>
       </c>
       <c r="B43" s="18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C43" s="19" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D43" s="17">
         <v>3</v>
       </c>
       <c r="E43" s="18" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F43" s="19" t="s">
         <v>10</v>
@@ -2283,7 +2286,7 @@
         <v>10</v>
       </c>
       <c r="C44" s="13" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D44" s="11">
         <f>SUM(D38:D43)</f>
@@ -2303,10 +2306,10 @@
         <v>7</v>
       </c>
       <c r="B45" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D45" s="1">
         <v>3</v>
@@ -2326,10 +2329,10 @@
         <v>7</v>
       </c>
       <c r="B46" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D46" s="1">
         <v>3</v>
@@ -2338,7 +2341,7 @@
         <v>13</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>10</v>
@@ -2349,16 +2352,16 @@
         <v>7</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C47" s="9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D47" s="8">
         <v>2</v>
       </c>
       <c r="E47" s="7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>10</v>
@@ -2372,16 +2375,16 @@
         <v>7</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C48" s="9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D48" s="8">
         <v>2</v>
       </c>
       <c r="E48" s="7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F48" s="9" t="s">
         <v>10</v>
@@ -2395,10 +2398,10 @@
         <v>7</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C49" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D49" s="8">
         <v>3</v>
@@ -2418,16 +2421,16 @@
         <v>7</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C50" s="9" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D50" s="8">
         <v>3</v>
       </c>
       <c r="E50" s="7" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F50" s="9" t="s">
         <v>10</v>
@@ -2444,7 +2447,7 @@
         <v>10</v>
       </c>
       <c r="C51" s="13" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D51" s="11">
         <f>SUM(D45:D50)</f>
@@ -2464,10 +2467,10 @@
         <v>8</v>
       </c>
       <c r="B52" s="15" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C52" s="16" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D52" s="14">
         <v>3</v>
@@ -2487,16 +2490,16 @@
         <v>8</v>
       </c>
       <c r="B53" s="18" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C53" s="19" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D53" s="17">
         <v>2</v>
       </c>
       <c r="E53" s="18" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F53" s="19" t="s">
         <v>10</v>
@@ -2510,16 +2513,16 @@
         <v>8</v>
       </c>
       <c r="B54" s="18" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C54" s="19" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D54" s="17">
         <v>2</v>
       </c>
       <c r="E54" s="18" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F54" s="19" t="s">
         <v>10</v>
@@ -2533,16 +2536,16 @@
         <v>8</v>
       </c>
       <c r="B55" s="18" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C55" s="19" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D55" s="17">
         <v>3</v>
       </c>
       <c r="E55" s="18" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F55" s="19" t="s">
         <v>10</v>
@@ -2605,7 +2608,7 @@
         <v>10</v>
       </c>
       <c r="C58" s="13" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D58" s="11">
         <f>SUM(D52:D57)</f>
@@ -2705,10 +2708,10 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D3" s="1">
         <v>3</v>
@@ -2866,16 +2869,16 @@
         <v>2</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D10" s="17">
         <v>3</v>
       </c>
       <c r="E10" s="18" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F10" s="19" t="s">
         <v>10</v>
@@ -2889,10 +2892,10 @@
         <v>2</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D11" s="14">
         <v>2</v>
@@ -2984,7 +2987,7 @@
         <v>10</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D15" s="11">
         <f>SUM(D8:D14)</f>
@@ -3004,10 +3007,10 @@
         <v>3</v>
       </c>
       <c r="B16" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D16" s="1">
         <v>1</v>
@@ -3085,7 +3088,7 @@
         <v>13</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>10</v>
@@ -3096,10 +3099,10 @@
         <v>3</v>
       </c>
       <c r="B20" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D20" s="1">
         <v>3</v>
@@ -3108,7 +3111,7 @@
         <v>13</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>10</v>
@@ -3119,10 +3122,10 @@
         <v>3</v>
       </c>
       <c r="B21" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D21" s="1">
         <v>3</v>
@@ -3145,7 +3148,7 @@
         <v>10</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D22" s="11">
         <f>SUM(D16:D21)</f>
@@ -3165,10 +3168,10 @@
         <v>4</v>
       </c>
       <c r="B23" s="15" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C23" s="16" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D23" s="14">
         <v>3</v>
@@ -3177,7 +3180,7 @@
         <v>13</v>
       </c>
       <c r="F23" s="16" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G23" s="16" t="s">
         <v>10</v>
@@ -3188,10 +3191,10 @@
         <v>4</v>
       </c>
       <c r="B24" s="15" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D24" s="14">
         <v>3</v>
@@ -3200,7 +3203,7 @@
         <v>13</v>
       </c>
       <c r="F24" s="16" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G24" s="16" t="s">
         <v>10</v>
@@ -3211,10 +3214,10 @@
         <v>4</v>
       </c>
       <c r="B25" s="15" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C25" s="16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D25" s="14">
         <v>3</v>
@@ -3223,7 +3226,7 @@
         <v>13</v>
       </c>
       <c r="F25" s="16" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G25" s="16" t="s">
         <v>10</v>
@@ -3234,10 +3237,10 @@
         <v>4</v>
       </c>
       <c r="B26" s="15" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C26" s="16" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D26" s="14">
         <v>2</v>
@@ -3246,7 +3249,7 @@
         <v>13</v>
       </c>
       <c r="F26" s="16" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G26" s="16" t="s">
         <v>10</v>
@@ -3257,10 +3260,10 @@
         <v>4</v>
       </c>
       <c r="B27" s="15" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C27" s="16" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D27" s="14">
         <v>3</v>
@@ -3269,7 +3272,7 @@
         <v>13</v>
       </c>
       <c r="F27" s="16" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G27" s="16" t="s">
         <v>10</v>
@@ -3280,10 +3283,10 @@
         <v>4</v>
       </c>
       <c r="B28" s="15" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C28" s="16" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D28" s="14">
         <v>3</v>
@@ -3292,7 +3295,7 @@
         <v>13</v>
       </c>
       <c r="F28" s="16" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G28" s="16" t="s">
         <v>10</v>
@@ -3306,7 +3309,7 @@
         <v>10</v>
       </c>
       <c r="C29" s="13" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D29" s="11">
         <f>SUM(D23:D28)</f>
@@ -3326,10 +3329,10 @@
         <v>5</v>
       </c>
       <c r="B30" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D30" s="1">
         <v>2</v>
@@ -3338,7 +3341,7 @@
         <v>13</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>10</v>
@@ -3349,10 +3352,10 @@
         <v>5</v>
       </c>
       <c r="B31" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D31" s="1">
         <v>3</v>
@@ -3361,7 +3364,7 @@
         <v>13</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>10</v>
@@ -3372,10 +3375,10 @@
         <v>5</v>
       </c>
       <c r="B32" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D32" s="1">
         <v>3</v>
@@ -3384,7 +3387,7 @@
         <v>13</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>10</v>
@@ -3395,10 +3398,10 @@
         <v>5</v>
       </c>
       <c r="B33" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D33" s="1">
         <v>3</v>
@@ -3407,7 +3410,7 @@
         <v>13</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>10</v>
@@ -3418,10 +3421,10 @@
         <v>5</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D34" s="8">
         <v>3</v>
@@ -3441,10 +3444,10 @@
         <v>5</v>
       </c>
       <c r="B35" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D35" s="1">
         <v>3</v>
@@ -3453,7 +3456,7 @@
         <v>13</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>10</v>
@@ -3467,7 +3470,7 @@
         <v>10</v>
       </c>
       <c r="C36" s="13" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D36" s="11">
         <f>SUM(D30:D35)</f>
@@ -3487,10 +3490,10 @@
         <v>6</v>
       </c>
       <c r="B37" s="15" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C37" s="16" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D37" s="14">
         <v>3</v>
@@ -3499,7 +3502,7 @@
         <v>13</v>
       </c>
       <c r="F37" s="16" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G37" s="16" t="s">
         <v>10</v>
@@ -3510,10 +3513,10 @@
         <v>6</v>
       </c>
       <c r="B38" s="15" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C38" s="16" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D38" s="14">
         <v>3</v>
@@ -3522,7 +3525,7 @@
         <v>13</v>
       </c>
       <c r="F38" s="16" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G38" s="16" t="s">
         <v>10</v>
@@ -3533,10 +3536,10 @@
         <v>6</v>
       </c>
       <c r="B39" s="15" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C39" s="16" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D39" s="14">
         <v>3</v>
@@ -3545,7 +3548,7 @@
         <v>13</v>
       </c>
       <c r="F39" s="16" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G39" s="16" t="s">
         <v>10</v>
@@ -3556,10 +3559,10 @@
         <v>6</v>
       </c>
       <c r="B40" s="15" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C40" s="16" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D40" s="14">
         <v>3</v>
@@ -3568,7 +3571,7 @@
         <v>13</v>
       </c>
       <c r="F40" s="16" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G40" s="16" t="s">
         <v>10</v>
@@ -3579,10 +3582,10 @@
         <v>6</v>
       </c>
       <c r="B41" s="15" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C41" s="16" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D41" s="14">
         <v>3</v>
@@ -3602,10 +3605,10 @@
         <v>6</v>
       </c>
       <c r="B42" s="15" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C42" s="16" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D42" s="14">
         <v>2</v>
@@ -3614,7 +3617,7 @@
         <v>13</v>
       </c>
       <c r="F42" s="16" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G42" s="16" t="s">
         <v>10</v>
@@ -3628,7 +3631,7 @@
         <v>10</v>
       </c>
       <c r="C43" s="13" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D43" s="11">
         <f>SUM(D37:D42)</f>
@@ -3648,10 +3651,10 @@
         <v>7</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D44" s="8">
         <v>3</v>
@@ -3671,10 +3674,10 @@
         <v>7</v>
       </c>
       <c r="B45" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D45" s="1">
         <v>3</v>
@@ -3694,10 +3697,10 @@
         <v>7</v>
       </c>
       <c r="B46" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D46" s="1">
         <v>3</v>
@@ -3706,7 +3709,7 @@
         <v>13</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>10</v>
@@ -3717,10 +3720,10 @@
         <v>7</v>
       </c>
       <c r="B47" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D47" s="1">
         <v>3</v>
@@ -3729,7 +3732,7 @@
         <v>13</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>10</v>
@@ -3740,16 +3743,16 @@
         <v>7</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C48" s="9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D48" s="8">
         <v>2</v>
       </c>
       <c r="E48" s="7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F48" s="9" t="s">
         <v>10</v>
@@ -3763,10 +3766,10 @@
         <v>7</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C49" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D49" s="8">
         <v>3</v>
@@ -3789,7 +3792,7 @@
         <v>10</v>
       </c>
       <c r="C50" s="13" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D50" s="11">
         <f>SUM(D44:D49)</f>
@@ -3809,10 +3812,10 @@
         <v>8</v>
       </c>
       <c r="B51" s="15" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C51" s="16" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D51" s="14">
         <v>3</v>
@@ -3832,16 +3835,16 @@
         <v>8</v>
       </c>
       <c r="B52" s="18" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C52" s="19" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D52" s="17">
         <v>2</v>
       </c>
       <c r="E52" s="18" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F52" s="19" t="s">
         <v>10</v>
@@ -3855,16 +3858,16 @@
         <v>8</v>
       </c>
       <c r="B53" s="18" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C53" s="19" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D53" s="17">
         <v>2</v>
       </c>
       <c r="E53" s="18" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F53" s="19" t="s">
         <v>10</v>
@@ -3878,16 +3881,16 @@
         <v>8</v>
       </c>
       <c r="B54" s="18" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C54" s="19" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D54" s="17">
         <v>2</v>
       </c>
       <c r="E54" s="18" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F54" s="19" t="s">
         <v>10</v>
@@ -3901,16 +3904,16 @@
         <v>8</v>
       </c>
       <c r="B55" s="18" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C55" s="19" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D55" s="17">
         <v>3</v>
       </c>
       <c r="E55" s="18" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F55" s="19" t="s">
         <v>10</v>
@@ -3973,7 +3976,7 @@
         <v>10</v>
       </c>
       <c r="C58" s="13" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D58" s="11">
         <f>SUM(D51:D57)</f>
@@ -4050,10 +4053,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D2" s="1">
         <v>3</v>
@@ -4292,7 +4295,7 @@
         <v>13</v>
       </c>
       <c r="F12" s="16" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G12" s="16" t="s">
         <v>10</v>
@@ -4303,10 +4306,10 @@
         <v>2</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D13" s="14">
         <v>3</v>
@@ -4315,7 +4318,7 @@
         <v>13</v>
       </c>
       <c r="F13" s="16" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G13" s="16" t="s">
         <v>10</v>
@@ -4352,7 +4355,7 @@
         <v>10</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D15" s="11">
         <f>SUM(D8:D14)</f>
@@ -4372,10 +4375,10 @@
         <v>3</v>
       </c>
       <c r="B16" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D16" s="1">
         <v>1</v>
@@ -4395,10 +4398,10 @@
         <v>3</v>
       </c>
       <c r="B17" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D17" s="1">
         <v>3</v>
@@ -4407,7 +4410,7 @@
         <v>13</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>10</v>
@@ -4418,10 +4421,10 @@
         <v>3</v>
       </c>
       <c r="B18" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D18" s="1">
         <v>3</v>
@@ -4430,7 +4433,7 @@
         <v>13</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>10</v>
@@ -4441,10 +4444,10 @@
         <v>3</v>
       </c>
       <c r="B19" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D19" s="1">
         <v>3</v>
@@ -4453,7 +4456,7 @@
         <v>13</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>10</v>
@@ -4464,10 +4467,10 @@
         <v>3</v>
       </c>
       <c r="B20" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D20" s="1">
         <v>2</v>
@@ -4476,7 +4479,7 @@
         <v>13</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>10</v>
@@ -4487,10 +4490,10 @@
         <v>3</v>
       </c>
       <c r="B21" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D21" s="1">
         <v>3</v>
@@ -4499,7 +4502,7 @@
         <v>13</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>10</v>
@@ -4536,7 +4539,7 @@
         <v>10</v>
       </c>
       <c r="C23" s="13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D23" s="11">
         <f>SUM(D16:D22)</f>
@@ -4556,10 +4559,10 @@
         <v>4</v>
       </c>
       <c r="B24" s="15" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D24" s="14">
         <v>2</v>
@@ -4568,7 +4571,7 @@
         <v>9</v>
       </c>
       <c r="F24" s="16" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G24" s="16" t="s">
         <v>10</v>
@@ -4579,10 +4582,10 @@
         <v>4</v>
       </c>
       <c r="B25" s="15" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C25" s="16" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D25" s="14">
         <v>3</v>
@@ -4591,7 +4594,7 @@
         <v>13</v>
       </c>
       <c r="F25" s="16" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G25" s="16" t="s">
         <v>10</v>
@@ -4602,10 +4605,10 @@
         <v>4</v>
       </c>
       <c r="B26" s="15" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C26" s="16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D26" s="14">
         <v>3</v>
@@ -4614,7 +4617,7 @@
         <v>13</v>
       </c>
       <c r="F26" s="16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G26" s="16" t="s">
         <v>10</v>
@@ -4625,10 +4628,10 @@
         <v>4</v>
       </c>
       <c r="B27" s="15" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C27" s="16" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D27" s="14">
         <v>3</v>
@@ -4637,7 +4640,7 @@
         <v>13</v>
       </c>
       <c r="F27" s="16" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G27" s="16" t="s">
         <v>10</v>
@@ -4648,10 +4651,10 @@
         <v>4</v>
       </c>
       <c r="B28" s="18" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C28" s="19" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D28" s="17">
         <v>3</v>
@@ -4671,10 +4674,10 @@
         <v>4</v>
       </c>
       <c r="B29" s="15" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C29" s="16" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D29" s="14">
         <v>2</v>
@@ -4697,7 +4700,7 @@
         <v>10</v>
       </c>
       <c r="C30" s="13" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D30" s="11">
         <f>SUM(D24:D29)</f>
@@ -4717,10 +4720,10 @@
         <v>5</v>
       </c>
       <c r="B31" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D31" s="1">
         <v>3</v>
@@ -4729,7 +4732,7 @@
         <v>13</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>10</v>
@@ -4740,10 +4743,10 @@
         <v>5</v>
       </c>
       <c r="B32" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D32" s="1">
         <v>3</v>
@@ -4752,7 +4755,7 @@
         <v>13</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>10</v>
@@ -4763,10 +4766,10 @@
         <v>5</v>
       </c>
       <c r="B33" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D33" s="1">
         <v>3</v>
@@ -4775,7 +4778,7 @@
         <v>13</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>10</v>
@@ -4786,10 +4789,10 @@
         <v>5</v>
       </c>
       <c r="B34" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D34" s="1">
         <v>3</v>
@@ -4798,7 +4801,7 @@
         <v>13</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>10</v>
@@ -4809,10 +4812,10 @@
         <v>5</v>
       </c>
       <c r="B35" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D35" s="1">
         <v>3</v>
@@ -4821,7 +4824,7 @@
         <v>13</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>10</v>
@@ -4832,10 +4835,10 @@
         <v>5</v>
       </c>
       <c r="B36" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D36" s="1">
         <v>3</v>
@@ -4858,7 +4861,7 @@
         <v>10</v>
       </c>
       <c r="C37" s="13" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D37" s="11">
         <f>SUM(D31:D36)</f>
@@ -4878,10 +4881,10 @@
         <v>6</v>
       </c>
       <c r="B38" s="15" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C38" s="16" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D38" s="14">
         <v>3</v>
@@ -4890,7 +4893,7 @@
         <v>9</v>
       </c>
       <c r="F38" s="16" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G38" s="16" t="s">
         <v>10</v>
@@ -4901,10 +4904,10 @@
         <v>6</v>
       </c>
       <c r="B39" s="15" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C39" s="16" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D39" s="14">
         <v>3</v>
@@ -4913,7 +4916,7 @@
         <v>13</v>
       </c>
       <c r="F39" s="16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G39" s="16" t="s">
         <v>10</v>
@@ -4924,10 +4927,10 @@
         <v>6</v>
       </c>
       <c r="B40" s="15" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C40" s="16" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D40" s="14">
         <v>3</v>
@@ -4936,7 +4939,7 @@
         <v>13</v>
       </c>
       <c r="F40" s="16" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G40" s="16" t="s">
         <v>10</v>
@@ -4947,10 +4950,10 @@
         <v>6</v>
       </c>
       <c r="B41" s="15" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C41" s="16" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D41" s="14">
         <v>3</v>
@@ -4959,7 +4962,7 @@
         <v>13</v>
       </c>
       <c r="F41" s="16" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G41" s="16" t="s">
         <v>10</v>
@@ -4970,10 +4973,10 @@
         <v>6</v>
       </c>
       <c r="B42" s="15" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C42" s="16" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D42" s="14">
         <v>2</v>
@@ -4993,16 +4996,16 @@
         <v>6</v>
       </c>
       <c r="B43" s="18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C43" s="19" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D43" s="17">
         <v>3</v>
       </c>
       <c r="E43" s="18" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F43" s="19" t="s">
         <v>10</v>
@@ -5019,7 +5022,7 @@
         <v>10</v>
       </c>
       <c r="C44" s="13" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D44" s="11">
         <f>SUM(D38:D43)</f>
@@ -5039,10 +5042,10 @@
         <v>7</v>
       </c>
       <c r="B45" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D45" s="1">
         <v>3</v>
@@ -5062,10 +5065,10 @@
         <v>7</v>
       </c>
       <c r="B46" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D46" s="1">
         <v>3</v>
@@ -5074,7 +5077,7 @@
         <v>13</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>10</v>
@@ -5085,10 +5088,10 @@
         <v>7</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C47" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D47" s="8">
         <v>3</v>
@@ -5108,16 +5111,16 @@
         <v>7</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C48" s="9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D48" s="8">
         <v>2</v>
       </c>
       <c r="E48" s="7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F48" s="9" t="s">
         <v>10</v>
@@ -5131,16 +5134,16 @@
         <v>7</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C49" s="9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D49" s="8">
         <v>2</v>
       </c>
       <c r="E49" s="7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>10</v>
@@ -5154,16 +5157,16 @@
         <v>7</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C50" s="9" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D50" s="8">
         <v>3</v>
       </c>
       <c r="E50" s="7" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F50" s="9" t="s">
         <v>10</v>
@@ -5180,7 +5183,7 @@
         <v>10</v>
       </c>
       <c r="C51" s="13" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D51" s="11">
         <f>SUM(D45:D50)</f>
@@ -5200,10 +5203,10 @@
         <v>8</v>
       </c>
       <c r="B52" s="15" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C52" s="16" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D52" s="14">
         <v>3</v>
@@ -5223,16 +5226,16 @@
         <v>8</v>
       </c>
       <c r="B53" s="18" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C53" s="19" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D53" s="17">
         <v>2</v>
       </c>
       <c r="E53" s="18" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F53" s="19" t="s">
         <v>10</v>
@@ -5246,16 +5249,16 @@
         <v>8</v>
       </c>
       <c r="B54" s="18" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C54" s="19" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D54" s="17">
         <v>2</v>
       </c>
       <c r="E54" s="18" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F54" s="19" t="s">
         <v>10</v>
@@ -5269,16 +5272,16 @@
         <v>8</v>
       </c>
       <c r="B55" s="18" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C55" s="19" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D55" s="17">
         <v>3</v>
       </c>
       <c r="E55" s="18" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F55" s="19" t="s">
         <v>10</v>
@@ -5341,7 +5344,7 @@
         <v>10</v>
       </c>
       <c r="C58" s="13" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D58" s="11">
         <f>SUM(D52:D57)</f>
@@ -5418,10 +5421,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D2" s="1">
         <v>3</v>
@@ -5441,10 +5444,10 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D3" s="1">
         <v>3</v>
@@ -5625,16 +5628,16 @@
         <v>2</v>
       </c>
       <c r="B11" s="18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D11" s="17">
         <v>3</v>
       </c>
       <c r="E11" s="18" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F11" s="19" t="s">
         <v>10</v>
@@ -5697,7 +5700,7 @@
         <v>10</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D14" s="11">
         <f>SUM(D8:D13)</f>
@@ -5717,10 +5720,10 @@
         <v>3</v>
       </c>
       <c r="B15" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D15" s="1">
         <v>1</v>
@@ -5763,10 +5766,10 @@
         <v>3</v>
       </c>
       <c r="B17" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D17" s="1">
         <v>2</v>
@@ -5821,7 +5824,7 @@
         <v>13</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>10</v>
@@ -5832,10 +5835,10 @@
         <v>3</v>
       </c>
       <c r="B20" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D20" s="1">
         <v>3</v>
@@ -5844,7 +5847,7 @@
         <v>13</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>10</v>
@@ -5855,10 +5858,10 @@
         <v>3</v>
       </c>
       <c r="B21" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D21" s="1">
         <v>3</v>
@@ -5881,7 +5884,7 @@
         <v>10</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D22" s="11">
         <f>SUM(D15:D21)</f>
@@ -5901,10 +5904,10 @@
         <v>4</v>
       </c>
       <c r="B23" s="15" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C23" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D23" s="14">
         <v>3</v>
@@ -5913,7 +5916,7 @@
         <v>13</v>
       </c>
       <c r="F23" s="16" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G23" s="16" t="s">
         <v>10</v>
@@ -5924,10 +5927,10 @@
         <v>4</v>
       </c>
       <c r="B24" s="15" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D24" s="14">
         <v>3</v>
@@ -5936,7 +5939,7 @@
         <v>13</v>
       </c>
       <c r="F24" s="16" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G24" s="16" t="s">
         <v>10</v>
@@ -5947,10 +5950,10 @@
         <v>4</v>
       </c>
       <c r="B25" s="15" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C25" s="16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D25" s="14">
         <v>3</v>
@@ -5959,7 +5962,7 @@
         <v>13</v>
       </c>
       <c r="F25" s="16" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G25" s="16" t="s">
         <v>10</v>
@@ -5970,10 +5973,10 @@
         <v>4</v>
       </c>
       <c r="B26" s="15" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C26" s="16" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D26" s="14">
         <v>2</v>
@@ -5982,7 +5985,7 @@
         <v>13</v>
       </c>
       <c r="F26" s="16" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G26" s="16" t="s">
         <v>10</v>
@@ -5993,10 +5996,10 @@
         <v>4</v>
       </c>
       <c r="B27" s="15" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C27" s="16" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D27" s="14">
         <v>3</v>
@@ -6005,7 +6008,7 @@
         <v>13</v>
       </c>
       <c r="F27" s="16" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G27" s="16" t="s">
         <v>10</v>
@@ -6016,10 +6019,10 @@
         <v>4</v>
       </c>
       <c r="B28" s="15" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C28" s="16" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D28" s="14">
         <v>3</v>
@@ -6028,7 +6031,7 @@
         <v>13</v>
       </c>
       <c r="F28" s="16" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G28" s="16" t="s">
         <v>10</v>
@@ -6042,7 +6045,7 @@
         <v>10</v>
       </c>
       <c r="C29" s="13" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D29" s="11">
         <f>SUM(D23:D28)</f>
@@ -6062,10 +6065,10 @@
         <v>5</v>
       </c>
       <c r="B30" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D30" s="1">
         <v>2</v>
@@ -6074,7 +6077,7 @@
         <v>9</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>10</v>
@@ -6085,10 +6088,10 @@
         <v>5</v>
       </c>
       <c r="B31" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D31" s="1">
         <v>3</v>
@@ -6097,7 +6100,7 @@
         <v>13</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>10</v>
@@ -6108,10 +6111,10 @@
         <v>5</v>
       </c>
       <c r="B32" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D32" s="1">
         <v>3</v>
@@ -6120,7 +6123,7 @@
         <v>13</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>10</v>
@@ -6131,10 +6134,10 @@
         <v>5</v>
       </c>
       <c r="B33" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D33" s="1">
         <v>3</v>
@@ -6143,7 +6146,7 @@
         <v>13</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>10</v>
@@ -6154,10 +6157,10 @@
         <v>5</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D34" s="8">
         <v>3</v>
@@ -6177,10 +6180,10 @@
         <v>5</v>
       </c>
       <c r="B35" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D35" s="1">
         <v>3</v>
@@ -6189,7 +6192,7 @@
         <v>13</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>10</v>
@@ -6203,7 +6206,7 @@
         <v>10</v>
       </c>
       <c r="C36" s="13" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D36" s="11">
         <f>SUM(D30:D35)</f>
@@ -6223,10 +6226,10 @@
         <v>6</v>
       </c>
       <c r="B37" s="15" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C37" s="16" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D37" s="14">
         <v>3</v>
@@ -6235,7 +6238,7 @@
         <v>13</v>
       </c>
       <c r="F37" s="16" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G37" s="16" t="s">
         <v>10</v>
@@ -6246,10 +6249,10 @@
         <v>6</v>
       </c>
       <c r="B38" s="15" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C38" s="16" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D38" s="14">
         <v>3</v>
@@ -6258,7 +6261,7 @@
         <v>13</v>
       </c>
       <c r="F38" s="16" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G38" s="16" t="s">
         <v>10</v>
@@ -6269,10 +6272,10 @@
         <v>6</v>
       </c>
       <c r="B39" s="15" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C39" s="16" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D39" s="14">
         <v>3</v>
@@ -6281,7 +6284,7 @@
         <v>13</v>
       </c>
       <c r="F39" s="16" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G39" s="16" t="s">
         <v>10</v>
@@ -6292,10 +6295,10 @@
         <v>6</v>
       </c>
       <c r="B40" s="15" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C40" s="16" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D40" s="14">
         <v>3</v>
@@ -6304,7 +6307,7 @@
         <v>13</v>
       </c>
       <c r="F40" s="16" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G40" s="16" t="s">
         <v>10</v>
@@ -6315,10 +6318,10 @@
         <v>6</v>
       </c>
       <c r="B41" s="15" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C41" s="16" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D41" s="14">
         <v>3</v>
@@ -6327,7 +6330,7 @@
         <v>13</v>
       </c>
       <c r="F41" s="16" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G41" s="16" t="s">
         <v>10</v>
@@ -6338,10 +6341,10 @@
         <v>6</v>
       </c>
       <c r="B42" s="15" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C42" s="16" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D42" s="14">
         <v>2</v>
@@ -6364,7 +6367,7 @@
         <v>10</v>
       </c>
       <c r="C43" s="13" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D43" s="11">
         <f>SUM(D37:D42)</f>
@@ -6384,10 +6387,10 @@
         <v>7</v>
       </c>
       <c r="B44" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D44" s="1">
         <v>3</v>
@@ -6396,7 +6399,7 @@
         <v>9</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>10</v>
@@ -6407,10 +6410,10 @@
         <v>7</v>
       </c>
       <c r="B45" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D45" s="1">
         <v>3</v>
@@ -6430,10 +6433,10 @@
         <v>7</v>
       </c>
       <c r="B46" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D46" s="1">
         <v>3</v>
@@ -6442,7 +6445,7 @@
         <v>13</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>10</v>
@@ -6453,10 +6456,10 @@
         <v>7</v>
       </c>
       <c r="B47" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D47" s="1">
         <v>3</v>
@@ -6465,7 +6468,7 @@
         <v>13</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>10</v>
@@ -6476,10 +6479,10 @@
         <v>7</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C48" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D48" s="8">
         <v>3</v>
@@ -6499,16 +6502,16 @@
         <v>7</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C49" s="9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D49" s="8">
         <v>2</v>
       </c>
       <c r="E49" s="7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>10</v>
@@ -6525,7 +6528,7 @@
         <v>10</v>
       </c>
       <c r="C50" s="13" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D50" s="11">
         <f>SUM(D44:D49)</f>
@@ -6545,10 +6548,10 @@
         <v>8</v>
       </c>
       <c r="B51" s="15" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C51" s="16" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D51" s="14">
         <v>3</v>
@@ -6568,16 +6571,16 @@
         <v>8</v>
       </c>
       <c r="B52" s="18" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C52" s="19" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D52" s="17">
         <v>2</v>
       </c>
       <c r="E52" s="18" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F52" s="19" t="s">
         <v>10</v>
@@ -6591,16 +6594,16 @@
         <v>8</v>
       </c>
       <c r="B53" s="18" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C53" s="19" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D53" s="17">
         <v>2</v>
       </c>
       <c r="E53" s="18" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F53" s="19" t="s">
         <v>10</v>
@@ -6614,16 +6617,16 @@
         <v>8</v>
       </c>
       <c r="B54" s="18" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C54" s="19" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D54" s="17">
         <v>2</v>
       </c>
       <c r="E54" s="18" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F54" s="19" t="s">
         <v>10</v>
@@ -6637,16 +6640,16 @@
         <v>8</v>
       </c>
       <c r="B55" s="18" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C55" s="19" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D55" s="17">
         <v>3</v>
       </c>
       <c r="E55" s="18" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F55" s="19" t="s">
         <v>10</v>
@@ -6709,7 +6712,7 @@
         <v>10</v>
       </c>
       <c r="C58" s="13" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D58" s="11">
         <f>SUM(D51:D57)</f>
@@ -6786,10 +6789,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D2" s="8">
         <v>3</v>
@@ -7028,7 +7031,7 @@
         <v>13</v>
       </c>
       <c r="F12" s="16" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G12" s="16" t="s">
         <v>10</v>
@@ -7039,10 +7042,10 @@
         <v>2</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D13" s="14">
         <v>3</v>
@@ -7051,7 +7054,7 @@
         <v>13</v>
       </c>
       <c r="F13" s="16" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G13" s="16" t="s">
         <v>10</v>
@@ -7088,7 +7091,7 @@
         <v>10</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D15" s="11">
         <f>SUM(D8:D14)</f>
@@ -7108,10 +7111,10 @@
         <v>3</v>
       </c>
       <c r="B16" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D16" s="1">
         <v>1</v>
@@ -7131,10 +7134,10 @@
         <v>3</v>
       </c>
       <c r="B17" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D17" s="1">
         <v>3</v>
@@ -7143,7 +7146,7 @@
         <v>13</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>10</v>
@@ -7154,10 +7157,10 @@
         <v>3</v>
       </c>
       <c r="B18" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D18" s="1">
         <v>3</v>
@@ -7166,7 +7169,7 @@
         <v>13</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>10</v>
@@ -7177,10 +7180,10 @@
         <v>3</v>
       </c>
       <c r="B19" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D19" s="1">
         <v>3</v>
@@ -7189,7 +7192,7 @@
         <v>13</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>10</v>
@@ -7200,10 +7203,10 @@
         <v>3</v>
       </c>
       <c r="B20" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D20" s="1">
         <v>2</v>
@@ -7212,7 +7215,7 @@
         <v>13</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>10</v>
@@ -7223,10 +7226,10 @@
         <v>3</v>
       </c>
       <c r="B21" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D21" s="1">
         <v>3</v>
@@ -7235,7 +7238,7 @@
         <v>13</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>10</v>
@@ -7272,7 +7275,7 @@
         <v>10</v>
       </c>
       <c r="C23" s="13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D23" s="11">
         <f>SUM(D16:D22)</f>
@@ -7292,10 +7295,10 @@
         <v>4</v>
       </c>
       <c r="B24" s="15" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D24" s="14">
         <v>2</v>
@@ -7304,7 +7307,7 @@
         <v>9</v>
       </c>
       <c r="F24" s="16" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G24" s="16" t="s">
         <v>10</v>
@@ -7315,10 +7318,10 @@
         <v>4</v>
       </c>
       <c r="B25" s="15" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C25" s="16" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D25" s="14">
         <v>3</v>
@@ -7327,7 +7330,7 @@
         <v>13</v>
       </c>
       <c r="F25" s="16" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G25" s="16" t="s">
         <v>10</v>
@@ -7338,10 +7341,10 @@
         <v>4</v>
       </c>
       <c r="B26" s="15" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C26" s="16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D26" s="14">
         <v>3</v>
@@ -7350,7 +7353,7 @@
         <v>13</v>
       </c>
       <c r="F26" s="16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G26" s="16" t="s">
         <v>10</v>
@@ -7361,10 +7364,10 @@
         <v>4</v>
       </c>
       <c r="B27" s="15" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C27" s="16" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D27" s="14">
         <v>3</v>
@@ -7373,7 +7376,7 @@
         <v>13</v>
       </c>
       <c r="F27" s="16" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G27" s="16" t="s">
         <v>10</v>
@@ -7384,10 +7387,10 @@
         <v>4</v>
       </c>
       <c r="B28" s="15" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C28" s="16" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D28" s="14">
         <v>2</v>
@@ -7407,10 +7410,10 @@
         <v>4</v>
       </c>
       <c r="B29" s="18" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C29" s="19" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D29" s="17">
         <v>3</v>
@@ -7430,10 +7433,10 @@
         <v>4</v>
       </c>
       <c r="B30" s="15" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C30" s="16" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D30" s="14">
         <v>2</v>
@@ -7456,7 +7459,7 @@
         <v>10</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D31" s="11">
         <f>SUM(D24:D30)</f>
@@ -7476,10 +7479,10 @@
         <v>5</v>
       </c>
       <c r="B32" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D32" s="1">
         <v>3</v>
@@ -7488,7 +7491,7 @@
         <v>13</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>10</v>
@@ -7499,10 +7502,10 @@
         <v>5</v>
       </c>
       <c r="B33" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D33" s="1">
         <v>3</v>
@@ -7511,7 +7514,7 @@
         <v>13</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>10</v>
@@ -7522,10 +7525,10 @@
         <v>5</v>
       </c>
       <c r="B34" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D34" s="1">
         <v>3</v>
@@ -7534,7 +7537,7 @@
         <v>13</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>10</v>
@@ -7545,10 +7548,10 @@
         <v>5</v>
       </c>
       <c r="B35" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D35" s="1">
         <v>3</v>
@@ -7557,7 +7560,7 @@
         <v>13</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>10</v>
@@ -7568,10 +7571,10 @@
         <v>5</v>
       </c>
       <c r="B36" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D36" s="1">
         <v>3</v>
@@ -7580,7 +7583,7 @@
         <v>13</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>10</v>
@@ -7591,10 +7594,10 @@
         <v>5</v>
       </c>
       <c r="B37" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D37" s="1">
         <v>3</v>
@@ -7617,7 +7620,7 @@
         <v>10</v>
       </c>
       <c r="C38" s="13" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D38" s="11">
         <f>SUM(D32:D37)</f>
@@ -7637,10 +7640,10 @@
         <v>6</v>
       </c>
       <c r="B39" s="15" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C39" s="16" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D39" s="14">
         <v>3</v>
@@ -7649,7 +7652,7 @@
         <v>9</v>
       </c>
       <c r="F39" s="16" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G39" s="16" t="s">
         <v>10</v>
@@ -7660,10 +7663,10 @@
         <v>6</v>
       </c>
       <c r="B40" s="15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C40" s="16" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D40" s="14">
         <v>3</v>
@@ -7672,7 +7675,7 @@
         <v>13</v>
       </c>
       <c r="F40" s="16" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G40" s="16" t="s">
         <v>10</v>
@@ -7683,10 +7686,10 @@
         <v>6</v>
       </c>
       <c r="B41" s="15" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C41" s="16" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D41" s="14">
         <v>3</v>
@@ -7695,7 +7698,7 @@
         <v>13</v>
       </c>
       <c r="F41" s="16" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="G41" s="16" t="s">
         <v>10</v>
@@ -7706,10 +7709,10 @@
         <v>6</v>
       </c>
       <c r="B42" s="15" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C42" s="16" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D42" s="14">
         <v>2</v>
@@ -7729,10 +7732,10 @@
         <v>6</v>
       </c>
       <c r="B43" s="15" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C43" s="16" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D43" s="14">
         <v>3</v>
@@ -7778,7 +7781,7 @@
         <v>10</v>
       </c>
       <c r="C45" s="13" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D45" s="11">
         <f>SUM(D39:D44)</f>
@@ -7798,10 +7801,10 @@
         <v>7</v>
       </c>
       <c r="B46" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D46" s="1">
         <v>3</v>
@@ -7821,10 +7824,10 @@
         <v>7</v>
       </c>
       <c r="B47" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D47" s="1">
         <v>3</v>
@@ -7833,7 +7836,7 @@
         <v>13</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>10</v>
@@ -7844,10 +7847,10 @@
         <v>7</v>
       </c>
       <c r="B48" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D48" s="1">
         <v>3</v>
@@ -7856,7 +7859,7 @@
         <v>13</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>10</v>
@@ -7867,16 +7870,16 @@
         <v>7</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C49" s="9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D49" s="8">
         <v>2</v>
       </c>
       <c r="E49" s="7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>10</v>
@@ -7890,16 +7893,16 @@
         <v>7</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C50" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D50" s="8">
         <v>3</v>
       </c>
       <c r="E50" s="7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F50" s="9" t="s">
         <v>10</v>
@@ -7913,10 +7916,10 @@
         <v>7</v>
       </c>
       <c r="B51" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D51" s="1">
         <v>2</v>
@@ -7925,7 +7928,7 @@
         <v>13</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>10</v>
@@ -7939,7 +7942,7 @@
         <v>10</v>
       </c>
       <c r="C52" s="13" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D52" s="11">
         <f>SUM(D46:D51)</f>
@@ -7959,10 +7962,10 @@
         <v>8</v>
       </c>
       <c r="B53" s="15" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C53" s="16" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D53" s="14">
         <v>3</v>
@@ -7982,10 +7985,10 @@
         <v>8</v>
       </c>
       <c r="B54" s="15" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C54" s="16" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D54" s="14">
         <v>3</v>
@@ -7994,7 +7997,7 @@
         <v>13</v>
       </c>
       <c r="F54" s="16" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G54" s="16" t="s">
         <v>10</v>
@@ -8005,10 +8008,10 @@
         <v>8</v>
       </c>
       <c r="B55" s="18" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C55" s="19" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D55" s="17">
         <v>3</v>
@@ -8028,16 +8031,16 @@
         <v>8</v>
       </c>
       <c r="B56" s="18" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C56" s="19" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D56" s="17">
         <v>2</v>
       </c>
       <c r="E56" s="18" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F56" s="19" t="s">
         <v>10</v>
@@ -8051,16 +8054,16 @@
         <v>8</v>
       </c>
       <c r="B57" s="18" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C57" s="19" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D57" s="17">
         <v>2</v>
       </c>
       <c r="E57" s="18" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F57" s="19" t="s">
         <v>10</v>
@@ -8074,16 +8077,16 @@
         <v>8</v>
       </c>
       <c r="B58" s="18" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C58" s="19" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D58" s="17">
         <v>2</v>
       </c>
       <c r="E58" s="18" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F58" s="19" t="s">
         <v>10</v>
@@ -8123,7 +8126,7 @@
         <v>10</v>
       </c>
       <c r="C60" s="13" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D60" s="11">
         <f>SUM(D53:D59)</f>
@@ -8143,10 +8146,10 @@
         <v>9</v>
       </c>
       <c r="B61" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D61" s="1">
         <v>3</v>
@@ -8166,16 +8169,16 @@
         <v>9</v>
       </c>
       <c r="B62" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C62" s="9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D62" s="8">
         <v>2</v>
       </c>
       <c r="E62" s="7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F62" s="9" t="s">
         <v>10</v>
@@ -8189,16 +8192,16 @@
         <v>9</v>
       </c>
       <c r="B63" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C63" s="9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D63" s="8">
         <v>2</v>
       </c>
       <c r="E63" s="7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>10</v>
@@ -8212,16 +8215,16 @@
         <v>9</v>
       </c>
       <c r="B64" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C64" s="9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D64" s="8">
         <v>2</v>
       </c>
       <c r="E64" s="7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F64" s="9" t="s">
         <v>10</v>
@@ -8235,16 +8238,16 @@
         <v>9</v>
       </c>
       <c r="B65" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C65" s="9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D65" s="8">
         <v>2</v>
       </c>
       <c r="E65" s="7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>10</v>
@@ -8261,7 +8264,7 @@
         <v>10</v>
       </c>
       <c r="C66" s="13" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D66" s="11">
         <f>SUM(D61:D65)</f>
@@ -8308,140 +8311,140 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="32" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B1" s="32" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C1" s="32" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D1" s="32" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E1" s="32" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F1" s="32" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G1" s="32" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C2" t="s">
         <v>10</v>
       </c>
       <c r="D2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="G3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C4" t="s">
         <v>10</v>
       </c>
       <c r="D4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="G4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B5" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C5" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D5" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E5" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G5" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
   </sheetData>
@@ -8469,33 +8472,33 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="32" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B1" s="32" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C1" s="33" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D1" s="32" t="s">
         <v>4</v>
       </c>
       <c r="E1" s="33" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>10</v>
@@ -8503,16 +8506,16 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>186</v>
+      </c>
+      <c r="B3" t="s">
+        <v>187</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="D3" t="s">
         <v>185</v>
-      </c>
-      <c r="B3" t="s">
-        <v>186</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="D3" t="s">
-        <v>184</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>10</v>
@@ -8520,16 +8523,16 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B4" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>10</v>
@@ -8563,54 +8566,54 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="32" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B1" s="32" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C1" s="34" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="32" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E1" s="32" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F1" s="32" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G1" s="32" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H1" s="33" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C2" s="1">
         <v>5</v>
       </c>
       <c r="D2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F2" t="s">
         <v>10</v>
       </c>
       <c r="G2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
   </sheetData>
@@ -8629,7 +8632,7 @@
   <sheetData>
     <row r="1" spans="1:1" s="35" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="35" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
@@ -8639,7 +8642,7 @@
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
@@ -8649,67 +8652,67 @@
     </row>
     <row r="5" spans="1:1" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="36" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
@@ -8719,37 +8722,37 @@
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
@@ -8759,22 +8762,22 @@
     </row>
     <row r="27" spans="1:1" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="36" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
   </sheetData>
